--- a/广东实时电价预测.xlsx
+++ b/广东实时电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="13580"/>
+    <workbookView windowWidth="29920" windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>日期</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3421,6 +3424,86 @@
         <v>317.45</v>
       </c>
     </row>
+    <row r="29" customFormat="1" spans="1:26">
+      <c r="A29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4">
+        <v>462.13</v>
+      </c>
+      <c r="D29" s="4">
+        <v>403.77</v>
+      </c>
+      <c r="E29" s="4">
+        <v>383.94</v>
+      </c>
+      <c r="F29" s="4">
+        <v>367.15</v>
+      </c>
+      <c r="G29" s="4">
+        <v>351.49</v>
+      </c>
+      <c r="H29" s="4">
+        <v>335.48</v>
+      </c>
+      <c r="I29" s="4">
+        <v>287.85</v>
+      </c>
+      <c r="J29" s="4">
+        <v>280.07</v>
+      </c>
+      <c r="K29" s="4">
+        <v>339</v>
+      </c>
+      <c r="L29" s="4">
+        <v>320.84</v>
+      </c>
+      <c r="M29" s="4">
+        <v>316.13</v>
+      </c>
+      <c r="N29" s="4">
+        <v>337.71</v>
+      </c>
+      <c r="O29" s="4">
+        <v>358.51</v>
+      </c>
+      <c r="P29" s="4">
+        <v>361.94</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>362.87</v>
+      </c>
+      <c r="R29" s="4">
+        <v>371.42</v>
+      </c>
+      <c r="S29" s="4">
+        <v>421.29</v>
+      </c>
+      <c r="T29" s="4">
+        <v>409.96</v>
+      </c>
+      <c r="U29" s="4">
+        <v>381.83</v>
+      </c>
+      <c r="V29" s="4">
+        <v>480.87</v>
+      </c>
+      <c r="W29" s="4">
+        <v>468</v>
+      </c>
+      <c r="X29" s="4">
+        <v>434.55</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>417.57</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>335.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东实时电价预测.xlsx
+++ b/广东实时电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
   <si>
     <t>日期</t>
   </si>
@@ -183,6 +183,21 @@
   </si>
   <si>
     <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3504,6 +3519,406 @@
         <v>335.46</v>
       </c>
     </row>
+    <row r="30" spans="1:26">
+      <c r="A30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="4">
+        <v>521.11</v>
+      </c>
+      <c r="D30" s="4">
+        <v>469.33</v>
+      </c>
+      <c r="E30" s="4">
+        <v>394.33</v>
+      </c>
+      <c r="F30" s="4">
+        <v>396.5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>371.84</v>
+      </c>
+      <c r="H30" s="4">
+        <v>374.57</v>
+      </c>
+      <c r="I30" s="4">
+        <v>329.54</v>
+      </c>
+      <c r="J30" s="4">
+        <v>320.23</v>
+      </c>
+      <c r="K30" s="4">
+        <v>360.55</v>
+      </c>
+      <c r="L30" s="4">
+        <v>378.39</v>
+      </c>
+      <c r="M30" s="4">
+        <v>375.33</v>
+      </c>
+      <c r="N30" s="4">
+        <v>439.08</v>
+      </c>
+      <c r="O30" s="4">
+        <v>387.71</v>
+      </c>
+      <c r="P30" s="4">
+        <v>450.69</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>409.81</v>
+      </c>
+      <c r="R30" s="4">
+        <v>414.66</v>
+      </c>
+      <c r="S30" s="4">
+        <v>445.34</v>
+      </c>
+      <c r="T30" s="4">
+        <v>424.54</v>
+      </c>
+      <c r="U30" s="4">
+        <v>378.66</v>
+      </c>
+      <c r="V30" s="4">
+        <v>470.14</v>
+      </c>
+      <c r="W30" s="4">
+        <v>453.8</v>
+      </c>
+      <c r="X30" s="4">
+        <v>480.05</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>411.89</v>
+      </c>
+      <c r="Z30" s="4">
+        <v>365.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="4">
+        <v>539.08</v>
+      </c>
+      <c r="D31" s="4">
+        <v>453.56</v>
+      </c>
+      <c r="E31" s="4">
+        <v>414.67</v>
+      </c>
+      <c r="F31" s="4">
+        <v>445.63</v>
+      </c>
+      <c r="G31" s="4">
+        <v>433.16</v>
+      </c>
+      <c r="H31" s="4">
+        <v>423.95</v>
+      </c>
+      <c r="I31" s="4">
+        <v>300.62</v>
+      </c>
+      <c r="J31" s="4">
+        <v>316.13</v>
+      </c>
+      <c r="K31" s="4">
+        <v>330.54</v>
+      </c>
+      <c r="L31" s="4">
+        <v>363.66</v>
+      </c>
+      <c r="M31" s="4">
+        <v>357.2</v>
+      </c>
+      <c r="N31" s="4">
+        <v>407.77</v>
+      </c>
+      <c r="O31" s="4">
+        <v>379.62</v>
+      </c>
+      <c r="P31" s="4">
+        <v>433.35</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>369.77</v>
+      </c>
+      <c r="R31" s="4">
+        <v>419.28</v>
+      </c>
+      <c r="S31" s="4">
+        <v>467.64</v>
+      </c>
+      <c r="T31" s="4">
+        <v>457.62</v>
+      </c>
+      <c r="U31" s="4">
+        <v>384.75</v>
+      </c>
+      <c r="V31" s="4">
+        <v>492.68</v>
+      </c>
+      <c r="W31" s="4">
+        <v>476.82</v>
+      </c>
+      <c r="X31" s="4">
+        <v>484.55</v>
+      </c>
+      <c r="Y31" s="4">
+        <v>421.19</v>
+      </c>
+      <c r="Z31" s="4">
+        <v>353.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="A32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="4">
+        <v>556.69</v>
+      </c>
+      <c r="D32" s="4">
+        <v>480.53</v>
+      </c>
+      <c r="E32" s="4">
+        <v>460.61</v>
+      </c>
+      <c r="F32" s="4">
+        <v>434.15</v>
+      </c>
+      <c r="G32" s="4">
+        <v>445.56</v>
+      </c>
+      <c r="H32" s="4">
+        <v>447.28</v>
+      </c>
+      <c r="I32" s="4">
+        <v>322.87</v>
+      </c>
+      <c r="J32" s="4">
+        <v>292.37</v>
+      </c>
+      <c r="K32" s="4">
+        <v>296.72</v>
+      </c>
+      <c r="L32" s="4">
+        <v>326.42</v>
+      </c>
+      <c r="M32" s="4">
+        <v>310.73</v>
+      </c>
+      <c r="N32" s="4">
+        <v>357.19</v>
+      </c>
+      <c r="O32" s="4">
+        <v>390.52</v>
+      </c>
+      <c r="P32" s="4">
+        <v>396.86</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>365.72</v>
+      </c>
+      <c r="R32" s="4">
+        <v>375.89</v>
+      </c>
+      <c r="S32" s="4">
+        <v>407.84</v>
+      </c>
+      <c r="T32" s="4">
+        <v>428.78</v>
+      </c>
+      <c r="U32" s="4">
+        <v>422.81</v>
+      </c>
+      <c r="V32" s="4">
+        <v>534.44</v>
+      </c>
+      <c r="W32" s="4">
+        <v>508.85</v>
+      </c>
+      <c r="X32" s="4">
+        <v>509.29</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>479.48</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>360.62</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:26">
+      <c r="A33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4">
+        <v>527.16</v>
+      </c>
+      <c r="D33" s="4">
+        <v>482.95</v>
+      </c>
+      <c r="E33" s="4">
+        <v>425.9</v>
+      </c>
+      <c r="F33" s="4">
+        <v>403.94</v>
+      </c>
+      <c r="G33" s="4">
+        <v>396.83</v>
+      </c>
+      <c r="H33" s="4">
+        <v>407.91</v>
+      </c>
+      <c r="I33" s="4">
+        <v>308.62</v>
+      </c>
+      <c r="J33" s="4">
+        <v>270.5</v>
+      </c>
+      <c r="K33" s="4">
+        <v>299.61</v>
+      </c>
+      <c r="L33" s="4">
+        <v>317.57</v>
+      </c>
+      <c r="M33" s="4">
+        <v>336.65</v>
+      </c>
+      <c r="N33" s="4">
+        <v>379.52</v>
+      </c>
+      <c r="O33" s="4">
+        <v>337.57</v>
+      </c>
+      <c r="P33" s="4">
+        <v>358.99</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>335.3</v>
+      </c>
+      <c r="R33" s="4">
+        <v>352.73</v>
+      </c>
+      <c r="S33" s="4">
+        <v>362.11</v>
+      </c>
+      <c r="T33" s="4">
+        <v>358.92</v>
+      </c>
+      <c r="U33" s="4">
+        <v>435.23</v>
+      </c>
+      <c r="V33" s="4">
+        <v>433.07</v>
+      </c>
+      <c r="W33" s="4">
+        <v>481.01</v>
+      </c>
+      <c r="X33" s="4">
+        <v>508.16</v>
+      </c>
+      <c r="Y33" s="4">
+        <v>441.1</v>
+      </c>
+      <c r="Z33" s="4">
+        <v>342.31</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:26">
+      <c r="A34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="4">
+        <v>446.9</v>
+      </c>
+      <c r="D34" s="4">
+        <v>448.97</v>
+      </c>
+      <c r="E34" s="4">
+        <v>374.23</v>
+      </c>
+      <c r="F34" s="4">
+        <v>356.89</v>
+      </c>
+      <c r="G34" s="4">
+        <v>321.07</v>
+      </c>
+      <c r="H34" s="4">
+        <v>326.49</v>
+      </c>
+      <c r="I34" s="4">
+        <v>284.94</v>
+      </c>
+      <c r="J34" s="4">
+        <v>281.82</v>
+      </c>
+      <c r="K34" s="4">
+        <v>334.41</v>
+      </c>
+      <c r="L34" s="4">
+        <v>337.17</v>
+      </c>
+      <c r="M34" s="4">
+        <v>323.81</v>
+      </c>
+      <c r="N34" s="4">
+        <v>335.06</v>
+      </c>
+      <c r="O34" s="4">
+        <v>345.33</v>
+      </c>
+      <c r="P34" s="4">
+        <v>365.94</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>365.58</v>
+      </c>
+      <c r="R34" s="4">
+        <v>372.56</v>
+      </c>
+      <c r="S34" s="4">
+        <v>406.96</v>
+      </c>
+      <c r="T34" s="4">
+        <v>423.88</v>
+      </c>
+      <c r="U34" s="4">
+        <v>399.4</v>
+      </c>
+      <c r="V34" s="4">
+        <v>479.25</v>
+      </c>
+      <c r="W34" s="4">
+        <v>444.05</v>
+      </c>
+      <c r="X34" s="4">
+        <v>425.79</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>412.76</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>327.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
